--- a/grupos/3BLCM - Estadisticos 20241.xlsx
+++ b/grupos/3BLCM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="162">
   <si>
     <t>Materia</t>
   </si>
@@ -212,18 +212,18 @@
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
@@ -242,262 +242,268 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>AMARO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
     <t>BAROJAS</t>
   </si>
   <si>
-    <t>ROMERO</t>
+    <t>BORBONIO</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>TENORIO</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>BORBONIO</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MAY</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>TENORIO</t>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSA</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>VIDAL</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>MANZANO</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>TELE</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>SALINAS</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSA</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>VIDAL</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>MANZANO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SALINAS</t>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>IRMA GUADALUPE</t>
   </si>
   <si>
     <t>ANGEL DANIEL</t>
   </si>
   <si>
-    <t>AXEL</t>
+    <t>BRENDA</t>
+  </si>
+  <si>
+    <t>HELI AIMEE</t>
+  </si>
+  <si>
+    <t>AYLIN AMADA</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>CARLOS OCTAVIO</t>
+  </si>
+  <si>
+    <t>ANGELICA</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>SINAI</t>
+  </si>
+  <si>
+    <t>ARANTZA NAHOMI</t>
+  </si>
+  <si>
+    <t>TATIANA</t>
+  </si>
+  <si>
+    <t>DANIA LIZETH</t>
+  </si>
+  <si>
+    <t>KENIA PAOLA</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>MELANY</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>MIRIAM NEFTALI</t>
+  </si>
+  <si>
+    <t>CINTHIA</t>
+  </si>
+  <si>
+    <t>MARYGELLI</t>
+  </si>
+  <si>
+    <t>ANGEL URIEL</t>
+  </si>
+  <si>
+    <t>KAREN AMERICA</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>LEYLA SARAI</t>
+  </si>
+  <si>
+    <t>LUZ MARIA</t>
+  </si>
+  <si>
+    <t>NOELIA</t>
+  </si>
+  <si>
+    <t>ABRIL AMAYRANI</t>
+  </si>
+  <si>
+    <t>VERONICA</t>
   </si>
   <si>
     <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>IRMA GUADALUPE</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
-    <t>HELI AIMEE</t>
-  </si>
-  <si>
-    <t>AYLIN AMADA</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>CARLOS OCTAVIO</t>
-  </si>
-  <si>
-    <t>ANGELICA</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>SINAI</t>
-  </si>
-  <si>
-    <t>ARANTZA NAHOMI</t>
-  </si>
-  <si>
-    <t>TATIANA</t>
-  </si>
-  <si>
-    <t>DANIA LIZETH</t>
-  </si>
-  <si>
-    <t>KENIA PAOLA</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>MELANY</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>MIRIAM NEFTALI</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>MARYGELLI</t>
-  </si>
-  <si>
-    <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>KAREN AMERICA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>LEYLA SARAI</t>
-  </si>
-  <si>
-    <t>LUZ MARIA</t>
-  </si>
-  <si>
-    <t>NOELIA</t>
-  </si>
-  <si>
-    <t>ABRIL AMAYRANI</t>
-  </si>
-  <si>
-    <t>VERONICA</t>
   </si>
 </sst>
 </file>
@@ -1043,28 +1049,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1091,22 +1097,22 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA4">
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>6</v>
       </c>
       <c r="AD4">
+        <v>8</v>
+      </c>
+      <c r="AE4">
         <v>6</v>
-      </c>
-      <c r="AE4">
-        <v>5</v>
       </c>
       <c r="AF4">
         <v>5</v>
@@ -1144,28 +1150,28 @@
         <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1192,22 +1198,22 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA5">
         <v>8</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF5">
         <v>9</v>
@@ -1245,28 +1251,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1299,7 +1305,7 @@
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC6">
         <v>10</v>
@@ -1346,28 +1352,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1400,19 +1406,19 @@
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE7">
         <v>7</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG7">
         <v>-1</v>
@@ -1447,28 +1453,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1501,7 +1507,7 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>9</v>
@@ -1548,28 +1554,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1602,7 +1608,7 @@
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>10</v>
@@ -1611,7 +1617,7 @@
         <v>10</v>
       </c>
       <c r="AE9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF9">
         <v>10</v>
@@ -1649,28 +1655,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1750,28 +1756,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1804,13 +1810,13 @@
         <v>8</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>10</v>
       </c>
       <c r="AD11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE11">
         <v>10</v>
@@ -1851,28 +1857,28 @@
         <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1905,13 +1911,13 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>7</v>
       </c>
       <c r="AD12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE12">
         <v>5</v>
@@ -1952,28 +1958,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -2006,16 +2012,16 @@
         <v>8</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC13">
         <v>8</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF13">
         <v>9</v>
@@ -2053,28 +2059,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -2110,13 +2116,13 @@
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD14">
         <v>10</v>
       </c>
       <c r="AE14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF14">
         <v>10</v>
@@ -2154,28 +2160,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2214,10 +2220,10 @@
         <v>5</v>
       </c>
       <c r="AD15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF15">
         <v>9</v>
@@ -2255,28 +2261,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2309,16 +2315,16 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD16">
         <v>10</v>
       </c>
       <c r="AE16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF16">
         <v>10</v>
@@ -2356,28 +2362,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2410,7 +2416,7 @@
         <v>10</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>10</v>
@@ -2457,28 +2463,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2511,13 +2517,13 @@
         <v>9</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE18">
         <v>10</v>
@@ -2558,28 +2564,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2612,13 +2618,13 @@
         <v>10</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE19">
         <v>10</v>
@@ -2659,28 +2665,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2713,7 +2719,7 @@
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC20">
         <v>9</v>
@@ -2760,28 +2766,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2814,13 +2820,13 @@
         <v>9</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE21">
         <v>9</v>
@@ -2861,28 +2867,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2918,13 +2924,13 @@
         <v>10</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD22">
+        <v>9</v>
+      </c>
+      <c r="AE22">
         <v>7</v>
-      </c>
-      <c r="AE22">
-        <v>8</v>
       </c>
       <c r="AF22">
         <v>10</v>
@@ -2962,28 +2968,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -3010,22 +3016,22 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA23">
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC23">
         <v>10</v>
       </c>
       <c r="AD23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF23">
         <v>10</v>
@@ -3063,28 +3069,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -3117,7 +3123,7 @@
         <v>8</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC24">
         <v>10</v>
@@ -3164,28 +3170,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3224,7 +3230,7 @@
         <v>10</v>
       </c>
       <c r="AD25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE25">
         <v>10</v>
@@ -3265,28 +3271,28 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3319,13 +3325,13 @@
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC26">
         <v>9</v>
       </c>
       <c r="AD26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE26">
         <v>10</v>
@@ -3366,28 +3372,28 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3429,7 +3435,7 @@
         <v>10</v>
       </c>
       <c r="AE27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF27">
         <v>10</v>
@@ -3467,28 +3473,28 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3521,7 +3527,7 @@
         <v>9</v>
       </c>
       <c r="AB28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC28">
         <v>8</v>
@@ -3568,28 +3574,28 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3622,13 +3628,13 @@
         <v>7</v>
       </c>
       <c r="AB29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC29">
         <v>9</v>
       </c>
       <c r="AD29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE29">
         <v>10</v>
@@ -3669,28 +3675,28 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3723,16 +3729,16 @@
         <v>8</v>
       </c>
       <c r="AB30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF30">
         <v>9</v>
@@ -3770,28 +3776,28 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3824,13 +3830,13 @@
         <v>7</v>
       </c>
       <c r="AB31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC31">
         <v>8</v>
       </c>
       <c r="AD31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE31">
         <v>8</v>
@@ -3871,28 +3877,28 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3925,16 +3931,16 @@
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF32">
         <v>10</v>
@@ -3972,28 +3978,28 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -4026,16 +4032,16 @@
         <v>8</v>
       </c>
       <c r="AB33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD33">
         <v>10</v>
       </c>
       <c r="AE33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF33">
         <v>10</v>
@@ -4073,28 +4079,28 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -4127,16 +4133,16 @@
         <v>7</v>
       </c>
       <c r="AB34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC34">
         <v>5</v>
       </c>
       <c r="AD34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF34">
         <v>8</v>
@@ -4174,28 +4180,28 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -4228,13 +4234,13 @@
         <v>10</v>
       </c>
       <c r="AB35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC35">
         <v>9</v>
       </c>
       <c r="AD35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE35">
         <v>10</v>
@@ -4275,28 +4281,28 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -4329,7 +4335,7 @@
         <v>8</v>
       </c>
       <c r="AB36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC36">
         <v>10</v>
@@ -4376,28 +4382,28 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -4430,16 +4436,16 @@
         <v>8</v>
       </c>
       <c r="AB37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC37">
+        <v>8</v>
+      </c>
+      <c r="AD37">
+        <v>8</v>
+      </c>
+      <c r="AE37">
         <v>7</v>
-      </c>
-      <c r="AD37">
-        <v>7</v>
-      </c>
-      <c r="AE37">
-        <v>9</v>
       </c>
       <c r="AF37">
         <v>10</v>
@@ -4477,28 +4483,28 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -4531,16 +4537,16 @@
         <v>8</v>
       </c>
       <c r="AB38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF38">
         <v>10</v>
@@ -4578,28 +4584,28 @@
         <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K39">
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -4632,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="AB39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC39">
         <v>10</v>
@@ -4679,28 +4685,28 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -4733,13 +4739,13 @@
         <v>8</v>
       </c>
       <c r="AB40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE40">
         <v>8</v>
@@ -4914,22 +4920,22 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>88.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -4938,22 +4944,22 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V4">
         <v>100</v>
       </c>
       <c r="W4">
-        <v>88.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X4">
         <v>100</v>
@@ -4991,52 +4997,52 @@
         <v>80</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M5">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S5">
         <v>100</v>
       </c>
       <c r="T5">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="U5">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V5">
         <v>100</v>
       </c>
       <c r="W5">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X5">
         <v>100</v>
       </c>
       <c r="Y5">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -5083,7 +5089,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -5107,7 +5113,7 @@
         <v>100</v>
       </c>
       <c r="W6">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X6">
         <v>100</v>
@@ -5145,7 +5151,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -5160,16 +5166,16 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P7">
-        <v>87</v>
+        <v>93.3</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -5184,10 +5190,10 @@
         <v>100</v>
       </c>
       <c r="W7">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X7">
-        <v>87</v>
+        <v>93.3</v>
       </c>
       <c r="Y7">
         <v>100</v>
@@ -5222,7 +5228,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -5237,7 +5243,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -5246,7 +5252,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -5261,7 +5267,7 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X8">
         <v>100</v>
@@ -5299,7 +5305,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -5323,7 +5329,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -5391,7 +5397,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -5415,7 +5421,7 @@
         <v>100</v>
       </c>
       <c r="W10">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X10">
         <v>100</v>
@@ -5468,7 +5474,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -5492,7 +5498,7 @@
         <v>100</v>
       </c>
       <c r="W11">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X11">
         <v>100</v>
@@ -5530,52 +5536,52 @@
         <v>80</v>
       </c>
       <c r="J12">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12">
+        <v>97</v>
+      </c>
+      <c r="M12">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="N12">
+        <v>56.3</v>
+      </c>
+      <c r="O12">
+        <v>69.7</v>
+      </c>
+      <c r="P12">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Q12">
         <v>90</v>
       </c>
-      <c r="K12">
-        <v>100</v>
-      </c>
-      <c r="L12">
-        <v>94</v>
-      </c>
-      <c r="M12">
-        <v>94.3</v>
-      </c>
-      <c r="N12">
-        <v>12.5</v>
-      </c>
-      <c r="O12">
-        <v>72.2</v>
-      </c>
-      <c r="P12">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="Q12">
-        <v>80</v>
-      </c>
       <c r="R12">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
+        <v>97</v>
+      </c>
+      <c r="U12">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="V12">
+        <v>56.3</v>
+      </c>
+      <c r="W12">
+        <v>69.7</v>
+      </c>
+      <c r="X12">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Y12">
         <v>90</v>
-      </c>
-      <c r="S12">
-        <v>100</v>
-      </c>
-      <c r="T12">
-        <v>94</v>
-      </c>
-      <c r="U12">
-        <v>94.3</v>
-      </c>
-      <c r="V12">
-        <v>12.5</v>
-      </c>
-      <c r="W12">
-        <v>72.2</v>
-      </c>
-      <c r="X12">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="Y12">
-        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -5761,49 +5767,49 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M15">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P15">
-        <v>87</v>
+        <v>93.3</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S15">
         <v>100</v>
       </c>
       <c r="T15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="U15">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="W15">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X15">
-        <v>87</v>
+        <v>93.3</v>
       </c>
       <c r="Y15">
         <v>100</v>
@@ -6084,7 +6090,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -6108,7 +6114,7 @@
         <v>100</v>
       </c>
       <c r="W19">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X19">
         <v>100</v>
@@ -6229,16 +6235,16 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="N21">
         <v>100</v>
       </c>
       <c r="O21">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -6253,16 +6259,16 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U21">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="V21">
         <v>100</v>
       </c>
       <c r="W21">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X21">
         <v>100</v>
@@ -6377,7 +6383,7 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -6401,7 +6407,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -6469,7 +6475,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -6493,7 +6499,7 @@
         <v>100</v>
       </c>
       <c r="W24">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X24">
         <v>100</v>
@@ -6531,7 +6537,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -6555,7 +6561,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -6608,7 +6614,7 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -6623,7 +6629,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -6632,7 +6638,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -6647,7 +6653,7 @@
         <v>100</v>
       </c>
       <c r="W26">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X26">
         <v>100</v>
@@ -6685,7 +6691,7 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -6709,7 +6715,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -6762,7 +6768,7 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -6771,13 +6777,13 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N28">
         <v>100</v>
       </c>
       <c r="O28">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -6786,7 +6792,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -6795,13 +6801,13 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V28">
         <v>100</v>
       </c>
       <c r="W28">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X28">
         <v>100</v>
@@ -6854,7 +6860,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -6878,7 +6884,7 @@
         <v>100</v>
       </c>
       <c r="W29">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X29">
         <v>100</v>
@@ -6916,7 +6922,7 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -6931,7 +6937,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -6940,7 +6946,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -6955,7 +6961,7 @@
         <v>100</v>
       </c>
       <c r="W30">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X30">
         <v>100</v>
@@ -6993,7 +6999,7 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -7017,7 +7023,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -7070,7 +7076,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -7085,7 +7091,7 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -7094,7 +7100,7 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -7109,7 +7115,7 @@
         <v>100</v>
       </c>
       <c r="W32">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X32">
         <v>100</v>
@@ -7162,7 +7168,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -7186,7 +7192,7 @@
         <v>100</v>
       </c>
       <c r="W33">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X33">
         <v>100</v>
@@ -7224,22 +7230,22 @@
         <v>100</v>
       </c>
       <c r="J34">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M34">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N34">
         <v>100</v>
       </c>
       <c r="O34">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -7248,22 +7254,22 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S34">
         <v>100</v>
       </c>
       <c r="T34">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U34">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V34">
         <v>100</v>
       </c>
       <c r="W34">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X34">
         <v>100</v>
@@ -7301,7 +7307,7 @@
         <v>100</v>
       </c>
       <c r="J35">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="K35">
         <v>100</v>
@@ -7316,7 +7322,7 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -7325,7 +7331,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -7340,7 +7346,7 @@
         <v>100</v>
       </c>
       <c r="W35">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X35">
         <v>100</v>
@@ -7470,7 +7476,7 @@
         <v>100</v>
       </c>
       <c r="O37">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -7494,7 +7500,7 @@
         <v>100</v>
       </c>
       <c r="W37">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X37">
         <v>100</v>
@@ -7532,7 +7538,7 @@
         <v>100</v>
       </c>
       <c r="J38">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="K38">
         <v>100</v>
@@ -7556,7 +7562,7 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="S38">
         <v>100</v>
@@ -7701,7 +7707,7 @@
         <v>100</v>
       </c>
       <c r="O40">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P40">
         <v>100</v>
@@ -7725,7 +7731,7 @@
         <v>100</v>
       </c>
       <c r="W40">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X40">
         <v>100</v>
@@ -7817,7 +7823,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -7826,19 +7832,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>89.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7849,7 +7855,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -7858,19 +7864,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>91.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>8.1</v>
+        <v>5.4</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7884,22 +7890,22 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5">
         <v>37</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>91.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>8.1</v>
+        <v>5.4</v>
       </c>
       <c r="H5">
         <v>8.6</v>
@@ -7913,28 +7919,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6">
         <v>37</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>94.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="G6" s="2">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7945,28 +7951,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>37</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>94.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="G7" s="2">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7986,19 +7992,19 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8080,7 +8086,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8112,22 +8118,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920118</v>
+        <v>23330051920144</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8135,16 +8141,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920118</v>
+        <v>23330051920144</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -8158,39 +8164,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920144</v>
+        <v>23330051920116</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920144</v>
+        <v>23330051920117</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -8204,39 +8210,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920150</v>
+        <v>23330051920118</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920150</v>
+        <v>23330061460223</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -8250,16 +8256,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920117</v>
+        <v>23330051920119</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -8273,16 +8279,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330061460223</v>
+        <v>23330051920120</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -8296,16 +8302,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920119</v>
+        <v>23330051920121</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -8319,16 +8325,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920120</v>
+        <v>23330051920124</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -8342,16 +8348,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920121</v>
+        <v>23330051920125</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -8365,16 +8371,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920124</v>
+        <v>23330051920126</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -8388,16 +8394,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920125</v>
+        <v>23330051920127</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -8411,16 +8417,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920126</v>
+        <v>23330051920128</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -8434,16 +8440,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920127</v>
+        <v>23330051920129</v>
       </c>
       <c r="B16" t="s">
         <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
@@ -8457,16 +8463,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920128</v>
+        <v>23330051920130</v>
       </c>
       <c r="B17" t="s">
         <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -8480,16 +8486,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920129</v>
+        <v>23330051920133</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -8503,16 +8509,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920130</v>
+        <v>23330051920134</v>
       </c>
       <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
         <v>85</v>
       </c>
-      <c r="C19" t="s">
-        <v>112</v>
-      </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
@@ -8526,16 +8532,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920133</v>
+        <v>23330051920135</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
@@ -8549,16 +8555,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920134</v>
+        <v>23330051920137</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
@@ -8572,16 +8578,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920135</v>
+        <v>23330051920122</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E22" t="s">
         <v>12</v>
@@ -8595,16 +8601,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920137</v>
+        <v>23330051920140</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
@@ -8618,16 +8624,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920122</v>
+        <v>23330051920139</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
@@ -8641,16 +8647,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920140</v>
+        <v>23330051920138</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E25" t="s">
         <v>12</v>
@@ -8664,16 +8670,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920139</v>
+        <v>23330051920255</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E26" t="s">
         <v>12</v>
@@ -8687,16 +8693,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920138</v>
+        <v>23330051920141</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
@@ -8710,16 +8716,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920255</v>
+        <v>23330051920315</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
@@ -8733,16 +8739,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920141</v>
+        <v>23330051920142</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E29" t="s">
         <v>12</v>
@@ -8756,16 +8762,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920315</v>
+        <v>23330051920143</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E30" t="s">
         <v>12</v>
@@ -8779,16 +8785,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920142</v>
+        <v>23330051920146</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E31" t="s">
         <v>12</v>
@@ -8802,16 +8808,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920143</v>
+        <v>23330051920147</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E32" t="s">
         <v>12</v>
@@ -8825,16 +8831,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920146</v>
+        <v>23330051920346</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E33" t="s">
         <v>12</v>
@@ -8848,16 +8854,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920147</v>
+        <v>23330051920148</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E34" t="s">
         <v>12</v>
@@ -8871,16 +8877,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920346</v>
+        <v>23330051920149</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E35" t="s">
         <v>12</v>
@@ -8894,16 +8900,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920148</v>
+        <v>23330051920150</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E36" t="s">
         <v>12</v>
@@ -8912,29 +8918,6 @@
         <v>63</v>
       </c>
       <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>23330051920149</v>
-      </c>
-      <c r="B37" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" t="s">
-        <v>159</v>
-      </c>
-      <c r="E37" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" t="s">
-        <v>63</v>
-      </c>
-      <c r="G37">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3BLCM - Estadisticos 20241.xlsx
+++ b/grupos/3BLCM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -215,15 +215,15 @@
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
@@ -242,6 +242,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
@@ -332,6 +335,9 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>VOTE</t>
+  </si>
+  <si>
     <t>NAVA</t>
   </si>
   <si>
@@ -402,6 +408,9 @@
   </si>
   <si>
     <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CAMILO</t>
   </si>
   <si>
     <t>AXEL</t>
@@ -1052,7 +1061,7 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -1100,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="AA4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>6</v>
@@ -1153,7 +1162,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -1201,7 +1210,7 @@
         <v>10</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <v>7</v>
@@ -1254,7 +1263,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1302,7 +1311,7 @@
         <v>10</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB6">
         <v>10</v>
@@ -1355,7 +1364,7 @@
         <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1456,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1504,7 +1513,7 @@
         <v>9</v>
       </c>
       <c r="AA8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB8">
         <v>9</v>
@@ -1557,7 +1566,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1605,7 +1614,7 @@
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB9">
         <v>10</v>
@@ -1658,7 +1667,7 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1759,7 +1768,7 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -1807,7 +1816,7 @@
         <v>10</v>
       </c>
       <c r="AA11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>9</v>
@@ -1860,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -1908,7 +1917,7 @@
         <v>9</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>6</v>
@@ -1961,7 +1970,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -2009,7 +2018,7 @@
         <v>10</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>8</v>
@@ -2062,7 +2071,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -2110,7 +2119,7 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>10</v>
@@ -2163,7 +2172,7 @@
         <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -2264,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -2312,7 +2321,7 @@
         <v>10</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB16">
         <v>10</v>
@@ -2365,7 +2374,7 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -2466,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -2567,7 +2576,7 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2668,7 +2677,7 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>9</v>
@@ -2716,7 +2725,7 @@
         <v>10</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB20">
         <v>8</v>
@@ -2769,7 +2778,7 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -2870,7 +2879,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2918,7 +2927,7 @@
         <v>10</v>
       </c>
       <c r="AA22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB22">
         <v>10</v>
@@ -2971,7 +2980,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -3019,7 +3028,7 @@
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB23">
         <v>10</v>
@@ -3072,7 +3081,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -3120,7 +3129,7 @@
         <v>10</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB24">
         <v>10</v>
@@ -3173,7 +3182,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -3274,7 +3283,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -3322,7 +3331,7 @@
         <v>10</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>9</v>
@@ -3375,7 +3384,7 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -3423,7 +3432,7 @@
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB27">
         <v>8</v>
@@ -3476,7 +3485,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -3524,7 +3533,7 @@
         <v>10</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB28">
         <v>9</v>
@@ -3577,7 +3586,7 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -3625,7 +3634,7 @@
         <v>10</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB29">
         <v>8</v>
@@ -3678,7 +3687,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -3726,7 +3735,7 @@
         <v>10</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB30">
         <v>8</v>
@@ -3779,7 +3788,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -3827,7 +3836,7 @@
         <v>10</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB31">
         <v>10</v>
@@ -3880,7 +3889,7 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>9</v>
@@ -3981,7 +3990,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -4029,7 +4038,7 @@
         <v>10</v>
       </c>
       <c r="AA33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB33">
         <v>8</v>
@@ -4082,7 +4091,7 @@
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>8</v>
@@ -4130,7 +4139,7 @@
         <v>10</v>
       </c>
       <c r="AA34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB34">
         <v>7</v>
@@ -4183,7 +4192,7 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -4284,7 +4293,7 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -4332,7 +4341,7 @@
         <v>10</v>
       </c>
       <c r="AA36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB36">
         <v>10</v>
@@ -4385,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
         <v>8</v>
@@ -4433,7 +4442,7 @@
         <v>10</v>
       </c>
       <c r="AA37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB37">
         <v>7</v>
@@ -4486,7 +4495,7 @@
         <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
         <v>10</v>
@@ -4534,7 +4543,7 @@
         <v>10</v>
       </c>
       <c r="AA38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB38">
         <v>9</v>
@@ -4587,7 +4596,7 @@
         <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
         <v>10</v>
@@ -4635,7 +4644,7 @@
         <v>10</v>
       </c>
       <c r="AA39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB39">
         <v>10</v>
@@ -4688,7 +4697,7 @@
         <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L40">
         <v>9</v>
@@ -4736,7 +4745,7 @@
         <v>10</v>
       </c>
       <c r="AA40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB40">
         <v>7</v>
@@ -7855,7 +7864,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -7876,7 +7885,7 @@
         <v>5.4</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7887,7 +7896,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
@@ -7896,19 +7905,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>94.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="G5" s="2">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7919,10 +7928,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6">
         <v>37</v>
@@ -7940,7 +7949,7 @@
         <v>2.7</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7951,28 +7960,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7">
         <v>37</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8086,7 +8095,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8118,22 +8127,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920144</v>
+        <v>22330061460232</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8141,16 +8150,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920144</v>
+        <v>22330061460232</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -8164,39 +8173,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920116</v>
+        <v>23330051920144</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920117</v>
+        <v>23330051920144</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -8210,16 +8219,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920118</v>
+        <v>23330051920116</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
         <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -8233,16 +8242,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330061460223</v>
+        <v>23330051920117</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -8256,16 +8265,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920119</v>
+        <v>23330051920118</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -8279,16 +8288,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920120</v>
+        <v>23330061460223</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -8302,16 +8311,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920121</v>
+        <v>23330051920119</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -8325,16 +8334,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920124</v>
+        <v>23330051920120</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -8348,16 +8357,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920125</v>
+        <v>23330051920121</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
         <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -8371,16 +8380,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920126</v>
+        <v>23330051920124</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -8394,16 +8403,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920127</v>
+        <v>23330051920125</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -8417,16 +8426,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920128</v>
+        <v>23330051920126</v>
       </c>
       <c r="B15" t="s">
         <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -8440,16 +8449,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920129</v>
+        <v>23330051920127</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
@@ -8463,16 +8472,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920130</v>
+        <v>23330051920128</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -8486,7 +8495,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920133</v>
+        <v>23330051920129</v>
       </c>
       <c r="B18" t="s">
         <v>86</v>
@@ -8495,7 +8504,7 @@
         <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -8509,16 +8518,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920134</v>
+        <v>23330051920130</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
@@ -8532,16 +8541,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920135</v>
+        <v>23330051920133</v>
       </c>
       <c r="B20" t="s">
         <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
@@ -8555,16 +8564,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920137</v>
+        <v>23330051920134</v>
       </c>
       <c r="B21" t="s">
         <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
@@ -8578,16 +8587,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920122</v>
+        <v>23330051920135</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
         <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E22" t="s">
         <v>12</v>
@@ -8601,16 +8610,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920140</v>
+        <v>23330051920137</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
@@ -8624,16 +8633,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920139</v>
+        <v>23330051920122</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
@@ -8647,16 +8656,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920138</v>
+        <v>23330051920140</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E25" t="s">
         <v>12</v>
@@ -8670,16 +8679,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920255</v>
+        <v>23330051920139</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
         <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E26" t="s">
         <v>12</v>
@@ -8693,16 +8702,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920141</v>
+        <v>23330051920138</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
         <v>120</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
@@ -8716,16 +8725,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920315</v>
+        <v>23330051920255</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
         <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
@@ -8739,16 +8748,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920142</v>
+        <v>23330051920141</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
         <v>122</v>
       </c>
       <c r="D29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E29" t="s">
         <v>12</v>
@@ -8762,16 +8771,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920143</v>
+        <v>23330051920315</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
         <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E30" t="s">
         <v>12</v>
@@ -8785,16 +8794,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920146</v>
+        <v>23330051920142</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E31" t="s">
         <v>12</v>
@@ -8808,16 +8817,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920147</v>
+        <v>23330051920143</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E32" t="s">
         <v>12</v>
@@ -8831,16 +8840,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920346</v>
+        <v>23330051920146</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E33" t="s">
         <v>12</v>
@@ -8854,16 +8863,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920148</v>
+        <v>23330051920147</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E34" t="s">
         <v>12</v>
@@ -8877,16 +8886,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920149</v>
+        <v>23330051920346</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E35" t="s">
         <v>12</v>
@@ -8900,16 +8909,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920150</v>
+        <v>23330051920148</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E36" t="s">
         <v>12</v>
@@ -8918,6 +8927,52 @@
         <v>63</v>
       </c>
       <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>23330051920149</v>
+      </c>
+      <c r="B37" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" t="s">
+        <v>163</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>23330051920150</v>
+      </c>
+      <c r="B38" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" t="s">
+        <v>164</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>63</v>
+      </c>
+      <c r="G38">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3BLCM - Estadisticos 20241.xlsx
+++ b/grupos/3BLCM - Estadisticos 20241.xlsx
@@ -221,7 +221,7 @@
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
+    <t>Martínez Marañon Mauricio</t>
   </si>
   <si>
     <t>Avila Coronado Julieta</t>

--- a/grupos/3BLCM - Estadisticos 20241.xlsx
+++ b/grupos/3BLCM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="82">
   <si>
     <t>Materia</t>
   </si>
@@ -209,21 +209,21 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>Martínez Marañon Mauricio</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -248,9 +248,6 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
@@ -260,16 +257,10 @@
     <t>SEGURA</t>
   </si>
   <si>
-    <t>VOTE</t>
-  </si>
-  <si>
     <t>JULIO EDUARDO</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>CAMILO</t>
   </si>
   <si>
     <t>AXEL</t>
@@ -820,10 +811,10 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -832,16 +823,16 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -853,13 +844,13 @@
         <v>6</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>6</v>
       </c>
       <c r="AC4">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -909,10 +900,10 @@
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -921,16 +912,16 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -948,7 +939,7 @@
         <v>8</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -998,10 +989,10 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1010,13 +1001,13 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1087,10 +1078,10 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1099,13 +1090,13 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1176,10 +1167,10 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1188,13 +1179,13 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1265,10 +1256,10 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1277,13 +1268,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1354,10 +1345,10 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1366,13 +1357,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1443,10 +1434,10 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1455,13 +1446,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1476,13 +1467,13 @@
         <v>10</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1532,10 +1523,10 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1544,13 +1535,13 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1565,13 +1556,13 @@
         <v>7</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB12">
         <v>5</v>
       </c>
       <c r="AC12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1621,10 +1612,10 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1633,13 +1624,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1710,10 +1701,10 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1722,13 +1713,13 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1749,7 +1740,7 @@
         <v>9</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1799,10 +1790,10 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1811,16 +1802,16 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1838,7 +1829,7 @@
         <v>7</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1888,10 +1879,10 @@
         <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1900,13 +1891,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1921,13 +1912,13 @@
         <v>8</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB16">
         <v>8</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1977,10 +1968,10 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -1989,13 +1980,13 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2066,10 +2057,10 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2078,13 +2069,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2099,7 +2090,7 @@
         <v>9</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB18">
         <v>10</v>
@@ -2155,10 +2146,10 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2167,13 +2158,13 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2194,7 +2185,7 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2244,10 +2235,10 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2256,13 +2247,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2277,13 +2268,13 @@
         <v>9</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB20">
         <v>10</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2333,10 +2324,10 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2345,13 +2336,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2422,10 +2413,10 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2434,13 +2425,13 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2461,7 +2452,7 @@
         <v>7</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2511,10 +2502,10 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2523,13 +2514,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2544,13 +2535,13 @@
         <v>10</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB23">
         <v>9</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2600,10 +2591,10 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2612,13 +2603,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2689,10 +2680,10 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2701,13 +2692,13 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2778,10 +2769,10 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2790,13 +2781,13 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2867,10 +2858,10 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2879,13 +2870,13 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2956,10 +2947,10 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2968,16 +2959,16 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -3045,10 +3036,10 @@
         <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3057,13 +3048,13 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -3134,10 +3125,10 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3146,13 +3137,13 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3223,10 +3214,10 @@
         <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3235,13 +3226,13 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3256,13 +3247,13 @@
         <v>8</v>
       </c>
       <c r="AA31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB31">
         <v>8</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3312,10 +3303,10 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3324,13 +3315,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3345,7 +3336,7 @@
         <v>9</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB32">
         <v>7</v>
@@ -3401,10 +3392,10 @@
         <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3413,13 +3404,13 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3440,7 +3431,7 @@
         <v>10</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3490,10 +3481,10 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3502,13 +3493,13 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3579,10 +3570,10 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3591,13 +3582,13 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>-1</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W35">
         <v>10</v>
@@ -3668,10 +3659,10 @@
         <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3680,13 +3671,13 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>-1</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>10</v>
@@ -3707,7 +3698,7 @@
         <v>10</v>
       </c>
       <c r="AC36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3757,10 +3748,10 @@
         <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3769,13 +3760,13 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>-1</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3796,7 +3787,7 @@
         <v>7</v>
       </c>
       <c r="AC37">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -3846,10 +3837,10 @@
         <v>9</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3858,13 +3849,13 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U38">
         <v>-1</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3885,7 +3876,7 @@
         <v>9</v>
       </c>
       <c r="AC38">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -3935,10 +3926,10 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -3947,13 +3938,13 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U39">
         <v>-1</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W39">
         <v>10</v>
@@ -4024,10 +4015,10 @@
         <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -4036,16 +4027,16 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U40">
         <v>-1</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X40">
         <v>9</v>
@@ -4063,7 +4054,7 @@
         <v>8</v>
       </c>
       <c r="AC40">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4235,7 +4226,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -4303,7 +4294,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -4439,7 +4430,7 @@
         <v>93.3</v>
       </c>
       <c r="P7">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -4457,7 +4448,7 @@
         <v>97</v>
       </c>
       <c r="V7">
-        <v>93.3</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4507,7 +4498,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4575,7 +4566,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -4643,7 +4634,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4779,7 +4770,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="P12">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4791,13 +4782,13 @@
         <v>97.09999999999999</v>
       </c>
       <c r="T12">
-        <v>56.3</v>
+        <v>70.8</v>
       </c>
       <c r="U12">
         <v>69.7</v>
       </c>
       <c r="V12">
-        <v>84.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4983,7 +4974,7 @@
         <v>93.3</v>
       </c>
       <c r="P15">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -5001,7 +4992,7 @@
         <v>97</v>
       </c>
       <c r="V15">
-        <v>93.3</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5459,7 +5450,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -5527,7 +5518,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5663,7 +5654,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5731,7 +5722,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5799,7 +5790,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5867,7 +5858,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -6003,7 +5994,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -6071,7 +6062,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -6139,7 +6130,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -6207,7 +6198,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -6275,7 +6266,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -6343,7 +6334,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -6547,7 +6538,7 @@
         <v>100</v>
       </c>
       <c r="P38">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -6758,7 +6749,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -6779,7 +6770,7 @@
         <v>5.4</v>
       </c>
       <c r="H2">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6790,7 +6781,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -6799,19 +6790,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>94.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="G3" s="2">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6822,7 +6813,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -6843,7 +6834,7 @@
         <v>2.7</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6857,7 +6848,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5">
         <v>37</v>
@@ -6886,7 +6877,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -6907,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6918,7 +6909,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -6939,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6971,7 +6962,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7041,7 +7032,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7079,13 +7070,13 @@
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>65</v>
@@ -7102,16 +7093,16 @@
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7125,16 +7116,16 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7148,16 +7139,16 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7165,47 +7156,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330061460232</v>
+        <v>23330051920144</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>63</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920144</v>
-      </c>
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BLCM - Estadisticos 20241.xlsx
+++ b/grupos/3BLCM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="77">
   <si>
     <t>Materia</t>
   </si>
@@ -209,21 +209,21 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
+    <t>Martínez Marañon Mauricio</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>Martínez Marañon Mauricio</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -245,25 +245,10 @@
     <t>COLMENARES</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
     <t>JULIO EDUARDO</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>AXEL</t>
   </si>
 </sst>
 </file>
@@ -817,16 +802,16 @@
         <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -841,13 +826,13 @@
         <v>6</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -906,16 +891,16 @@
         <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -927,16 +912,16 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA5">
         <v>8</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>8</v>
@@ -995,16 +980,16 @@
         <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1084,16 +1069,16 @@
         <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1105,16 +1090,16 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1173,16 +1158,16 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1262,16 +1247,16 @@
         <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>10</v>
@@ -1351,16 +1336,16 @@
         <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>10</v>
@@ -1440,16 +1425,16 @@
         <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1529,16 +1514,16 @@
         <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1550,10 +1535,10 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>5</v>
@@ -1618,16 +1603,16 @@
         <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1707,16 +1692,16 @@
         <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1731,7 +1716,7 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA14">
         <v>10</v>
@@ -1796,16 +1781,16 @@
         <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1817,10 +1802,10 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>7</v>
@@ -1885,16 +1870,16 @@
         <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1909,7 +1894,7 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16">
         <v>9</v>
@@ -1974,16 +1959,16 @@
         <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -2063,16 +2048,16 @@
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -2152,16 +2137,16 @@
         <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2173,7 +2158,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2241,16 +2226,16 @@
         <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2330,16 +2315,16 @@
         <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2354,7 +2339,7 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>9</v>
@@ -2419,16 +2404,16 @@
         <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2440,16 +2425,16 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>9</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC22">
         <v>9</v>
@@ -2508,16 +2493,16 @@
         <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2597,16 +2582,16 @@
         <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>10</v>
@@ -2686,16 +2671,16 @@
         <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2775,16 +2760,16 @@
         <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2796,7 +2781,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z26">
         <v>9</v>
@@ -2864,16 +2849,16 @@
         <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2953,16 +2938,16 @@
         <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -3042,16 +3027,16 @@
         <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>10</v>
@@ -3131,16 +3116,16 @@
         <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>9</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -3155,7 +3140,7 @@
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA30">
         <v>9</v>
@@ -3220,16 +3205,16 @@
         <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3241,7 +3226,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z31">
         <v>8</v>
@@ -3309,16 +3294,16 @@
         <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
         <v>7</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3330,16 +3315,16 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>10</v>
@@ -3398,16 +3383,16 @@
         <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>9</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>9</v>
@@ -3487,16 +3472,16 @@
         <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>9</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
         <v>9</v>
@@ -3508,16 +3493,16 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>8</v>
       </c>
       <c r="AB34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC34">
         <v>8</v>
@@ -3576,16 +3561,16 @@
         <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>9</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3665,16 +3650,16 @@
         <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <v>9</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3754,16 +3739,16 @@
         <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>7</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
         <v>9</v>
@@ -3784,7 +3769,7 @@
         <v>8</v>
       </c>
       <c r="AB37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC37">
         <v>9</v>
@@ -3843,16 +3828,16 @@
         <v>9</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>9</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
         <v>9</v>
@@ -3932,16 +3917,16 @@
         <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>9</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
         <v>10</v>
@@ -4021,16 +4006,16 @@
         <v>9</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
         <v>8</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V40">
         <v>9</v>
@@ -4232,16 +4217,16 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="S4">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T4">
         <v>100</v>
       </c>
       <c r="U4">
-        <v>87.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -4300,16 +4285,16 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S5">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T5">
         <v>100</v>
       </c>
       <c r="U5">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4377,7 +4362,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -4445,7 +4430,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V7">
         <v>95.2</v>
@@ -4513,7 +4498,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4649,7 +4634,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -4717,7 +4702,7 @@
         <v>100</v>
       </c>
       <c r="U11">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -4776,16 +4761,16 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>97</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S12">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T12">
         <v>70.8</v>
       </c>
       <c r="U12">
-        <v>69.7</v>
+        <v>75</v>
       </c>
       <c r="V12">
         <v>88.90000000000001</v>
@@ -4844,7 +4829,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4853,7 +4838,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4980,16 +4965,16 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S15">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T15">
         <v>100</v>
       </c>
       <c r="U15">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V15">
         <v>95.2</v>
@@ -5057,7 +5042,7 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -5125,7 +5110,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -5193,7 +5178,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5261,7 +5246,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -5329,7 +5314,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -5388,16 +5373,16 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S21">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T21">
         <v>100</v>
       </c>
       <c r="U21">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -5459,13 +5444,13 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T22">
         <v>100</v>
       </c>
       <c r="U22">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -5601,7 +5586,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -5669,7 +5654,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5737,7 +5722,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -5805,7 +5790,7 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5867,13 +5852,13 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="T28">
         <v>100</v>
       </c>
       <c r="U28">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5941,7 +5926,7 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6009,7 +5994,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -6077,7 +6062,7 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -6136,16 +6121,16 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T32">
         <v>100</v>
       </c>
       <c r="U32">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -6213,7 +6198,7 @@
         <v>100</v>
       </c>
       <c r="U33">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -6272,16 +6257,16 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S34">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T34">
         <v>100</v>
       </c>
       <c r="U34">
-        <v>97</v>
+        <v>93.8</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -6349,7 +6334,7 @@
         <v>100</v>
       </c>
       <c r="U35">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V35">
         <v>100</v>
@@ -6417,7 +6402,7 @@
         <v>100</v>
       </c>
       <c r="U36">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V36">
         <v>100</v>
@@ -6485,7 +6470,7 @@
         <v>100</v>
       </c>
       <c r="U37">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V37">
         <v>100</v>
@@ -6553,7 +6538,7 @@
         <v>100</v>
       </c>
       <c r="U38">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V38">
         <v>100</v>
@@ -6621,7 +6606,7 @@
         <v>100</v>
       </c>
       <c r="U39">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V39">
         <v>100</v>
@@ -6680,16 +6665,16 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S40">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T40">
         <v>100</v>
       </c>
       <c r="U40">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V40">
         <v>100</v>
@@ -6749,7 +6734,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -6758,19 +6743,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>94.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="G2" s="2">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6781,7 +6766,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -6802,7 +6787,7 @@
         <v>2.7</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6813,7 +6798,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -6822,19 +6807,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6845,28 +6830,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C5">
         <v>37</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6877,10 +6862,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6">
         <v>37</v>
@@ -6898,7 +6883,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6909,7 +6894,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -6930,7 +6915,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7032,7 +7017,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7070,16 +7055,16 @@
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7093,87 +7078,18 @@
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920404</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920404</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920144</v>
-      </c>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>
